--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -2807,7 +2807,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="419">
+  <borders count="426">
     <border>
       <left/>
       <right/>
@@ -2818,6 +2818,8 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -3591,6 +3593,9 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -4949,6 +4954,8 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
     <border/>
     <border/>
     <border/>
@@ -5691,1650 +5698,1657 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="419">
+  <cellXfs count="426">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0"/>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="330" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="340" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="346" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="352" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="358" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="374" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="378" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="379" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0"/>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="380" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="381" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="382" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="399" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="402" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="404" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="407" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="408" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="409" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="410" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="411" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="412" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="413" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="414" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="415" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="416" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="417" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="418" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="419" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="420" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="422" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="423" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="425" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="426" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="427" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="428" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="429" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="430" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="431" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="432" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="433" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="434" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="435" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="436" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="437" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="438" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="440" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="441" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="442" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="443" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="444" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="446" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="450" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="451" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="452" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="453" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="455" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="456" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="458" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="460" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="461" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="462" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="464" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="465" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="466" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="467" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="468" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="470" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="471" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="472" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="474" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="476" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="311" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="312" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" xfId="0"/>
-    <xf numFmtId="0" fontId="478" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="480" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="482" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="484" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="486" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="488" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="490" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="492" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="494" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="496" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="498" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="500" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="502" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="504" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="506" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="508" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="510" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="512" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="514" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="516" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="518" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="520" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="522" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="524" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="526" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="528" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="530" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="532" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="534" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="584" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="586" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="588" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="589" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" xfId="0"/>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="590" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="591" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="593" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="595" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="597" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="601" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="612" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="627" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="628" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="630" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="632" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="634" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="636" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="638" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="639" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="640" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="641" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7352,181 +7366,183 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="22.7109375" style="2" customWidth="true"/>
-    <col min="3" max="5" width="18.7109375" style="3" customWidth="true"/>
+    <col min="3" max="3" width="18.7109375" style="3" customWidth="true"/>
+    <col min="4" max="4" width="18.7109375" style="4" customWidth="true"/>
+    <col min="5" max="5" width="18.7109375" style="5" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="54" t="s">
+      <c r="B1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="56" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="76" t="s">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="80" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="83" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="86" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="86" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="87" t="s">
+      <c r="C5" s="87" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="89" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="30" t="s">
+      <c r="A6" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="92" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="92" t="s">
+      <c r="D7" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="93" t="s">
+      <c r="E7" s="95" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="95" t="s">
+      <c r="D8" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="96" t="s">
+      <c r="E8" s="98" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="45" t="s">
+      <c r="A9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="99" t="s">
+      <c r="E9" s="101" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="108" t="s">
+      <c r="A10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="103" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="103" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="103" t="s">
+      <c r="C10" s="105" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="105" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="105" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="113" t="s">
+      <c r="B11" s="115" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="2"/>
@@ -7547,339 +7563,342 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="114" customWidth="true"/>
-    <col min="2" max="2" width="22.7109375" style="115" customWidth="true"/>
-    <col min="3" max="6" width="18.7109375" style="116" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="116" customWidth="true"/>
+    <col min="2" max="2" width="22.7109375" style="117" customWidth="true"/>
+    <col min="3" max="3" width="18.7109375" style="118" customWidth="true"/>
+    <col min="4" max="4" width="18.7109375" style="119" customWidth="true"/>
+    <col min="5" max="5" width="18.7109375" style="120" customWidth="true"/>
+    <col min="6" max="6" width="18.7109375" style="121" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="227" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="213" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="213" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="213" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="213" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="213" t="s">
+      <c r="B1" s="218" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="218" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="218" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="218" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="218" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="238" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="239" t="s">
+      <c r="A2" s="128" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="243" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="244" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="240" t="s">
+      <c r="D2" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="241" t="s">
+      <c r="E2" s="246" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="242" t="s">
+      <c r="F2" s="247" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="129" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="130" t="s">
+      <c r="A3" s="134" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="248" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="244" t="s">
+      <c r="D3" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="245" t="s">
+      <c r="E3" s="250" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="246" t="s">
+      <c r="F3" s="251" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="135" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="136" t="s">
+      <c r="A4" s="140" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="247" t="s">
+      <c r="C4" s="252" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="248" t="s">
+      <c r="D4" s="253" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="249" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="250" t="s">
+      <c r="E4" s="254" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="255" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="141" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="142" t="s">
+      <c r="A5" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="147" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="251" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="252" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="253" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="254" t="s">
+      <c r="C5" s="256" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="257" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="258" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="259" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="147" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="148" t="s">
+      <c r="A6" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="153" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="255" t="s">
+      <c r="C6" s="260" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="256" t="s">
+      <c r="D6" s="261" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="257" t="s">
+      <c r="E6" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="258" t="s">
+      <c r="F6" s="263" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="153" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="154" t="s">
+      <c r="A7" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="259" t="s">
+      <c r="C7" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="260" t="s">
+      <c r="D7" s="265" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="261" t="s">
+      <c r="E7" s="266" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="262" t="s">
+      <c r="F7" s="267" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="159" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="160" t="s">
+      <c r="A8" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="263" t="s">
+      <c r="C8" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="264" t="s">
+      <c r="D8" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="265" t="s">
+      <c r="E8" s="270" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="266" t="s">
+      <c r="F8" s="271" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="165" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="166" t="s">
+      <c r="A9" s="170" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="272" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="268" t="s">
+      <c r="D9" s="273" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="269" t="s">
+      <c r="E9" s="274" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="270" t="s">
+      <c r="F9" s="275" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="171" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="172" t="s">
+      <c r="A10" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="177" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="271" t="s">
+      <c r="C10" s="276" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="272" t="s">
+      <c r="D10" s="277" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="273" t="s">
+      <c r="E10" s="278" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="274" t="s">
+      <c r="F10" s="279" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="177" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="178" t="s">
+      <c r="A11" s="182" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="275" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="276" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="277" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="278" t="s">
+      <c r="C11" s="280" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="281" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="282" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="283" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="183" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="184" t="s">
+      <c r="A12" s="188" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="279" t="s">
+      <c r="C12" s="284" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="280" t="s">
+      <c r="D12" s="285" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="281" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="282" t="s">
+      <c r="E12" s="286" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="287" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="189" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="190" t="s">
+      <c r="A13" s="194" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="283" t="s">
+      <c r="C13" s="288" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="284" t="s">
+      <c r="D13" s="289" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="285" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="286" t="s">
+      <c r="E13" s="290" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="291" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="195" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="196" t="s">
+      <c r="A14" s="200" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="287" t="s">
+      <c r="C14" s="292" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="288" t="s">
+      <c r="D14" s="293" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="289" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="290" t="s">
+      <c r="E14" s="294" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="295" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="201" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="202" t="s">
+      <c r="A15" s="206" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="207" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="291" t="s">
+      <c r="C15" s="296" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="292" t="s">
+      <c r="D15" s="297" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="293" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="294" t="s">
+      <c r="E15" s="298" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="299" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="305" t="s">
+      <c r="A16" s="212" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="310" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="299" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="299" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="299" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="299" t="s">
+      <c r="C16" s="304" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="304" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="304" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="304" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="310" t="s">
+      <c r="B17" s="315" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7895,178 +7914,180 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="311" customWidth="true"/>
-    <col min="2" max="2" width="22.7109375" style="312" customWidth="true"/>
-    <col min="3" max="5" width="18.7109375" style="313" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="316" customWidth="true"/>
+    <col min="2" max="2" width="22.7109375" style="317" customWidth="true"/>
+    <col min="3" max="3" width="18.7109375" style="318" customWidth="true"/>
+    <col min="4" max="4" width="18.7109375" style="319" customWidth="true"/>
+    <col min="5" max="5" width="18.7109375" style="320" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="372" t="s">
+      <c r="A1" s="379" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="364" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="364" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="364" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="364" t="s">
+      <c r="B1" s="371" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="371" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="371" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="371" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="319" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="385" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="386" t="s">
+      <c r="A2" s="326" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="392" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="393" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="387" t="s">
+      <c r="D2" s="394" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="388" t="s">
+      <c r="E2" s="395" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="324" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="325" t="s">
+      <c r="A3" s="331" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="332" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="389" t="s">
+      <c r="C3" s="396" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="390" t="s">
+      <c r="D3" s="397" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="391" t="s">
+      <c r="E3" s="398" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="329" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="330" t="s">
+      <c r="A4" s="336" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="337" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="392" t="s">
+      <c r="C4" s="399" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="393" t="s">
+      <c r="D4" s="400" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="394" t="s">
+      <c r="E4" s="401" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="334" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="335" t="s">
+      <c r="A5" s="341" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="342" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="395" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="396" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="397" t="s">
+      <c r="C5" s="402" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="403" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="404" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="339" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="340" t="s">
+      <c r="A6" s="346" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="347" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="398" t="s">
+      <c r="C6" s="405" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="399" t="s">
+      <c r="D6" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="400" t="s">
+      <c r="E6" s="407" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="344" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="345" t="s">
+      <c r="A7" s="351" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="352" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="401" t="s">
+      <c r="C7" s="408" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="402" t="s">
+      <c r="D7" s="409" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="403" t="s">
+      <c r="E7" s="410" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="349" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="350" t="s">
+      <c r="A8" s="356" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="357" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="404" t="s">
+      <c r="C8" s="411" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="405" t="s">
+      <c r="D8" s="412" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="406" t="s">
+      <c r="E8" s="413" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="354" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="355" t="s">
+      <c r="A9" s="361" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="362" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="407" t="s">
+      <c r="C9" s="414" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="408" t="s">
+      <c r="D9" s="415" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="409" t="s">
+      <c r="E9" s="416" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="359" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="418" t="s">
+      <c r="A10" s="366" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="425" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="413" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="413" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="413" t="s">
+      <c r="C10" s="420" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="420" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="420" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -152,7 +152,7 @@
     <t>-0.2 (-0.8, 0.3)</t>
   </si>
   <si>
-    <t>-0.88</t>
+    <t>-0.88 (-3.76, 1.99)</t>
   </si>
   <si>
     <t>RMST = restricted mean survival time truncated at 1460 days.</t>

--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="198" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="188" uniqueCount="56">
   <si>
     <t>Table 18. Kaplan-Meier Survival Estimates</t>
   </si>
@@ -189,7 +189,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="642">
+  <fonts count="616">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2125,86 +2125,6 @@
       <sz val="8"/>
       <name val="Arial"/>
       <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2676,30 +2596,6 @@
     <font>
       <sz val="12"/>
       <b/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -2807,7 +2703,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="426">
+  <borders count="410">
     <border>
       <left/>
       <right/>
@@ -5305,76 +5201,6 @@
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
       <top style="medium"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -5482,48 +5308,6 @@
       <right style="none"/>
       <top style="medium"/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -5698,7 +5482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="426">
+  <cellXfs count="410">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -7116,239 +6900,175 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="584" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="586" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="588" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="589" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="590" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="591" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="593" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="595" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="597" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="601" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="612" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="627" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="628" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="630" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="632" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="634" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="636" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="638" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="639" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="640" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="641" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7911,7 +7631,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="316" customWidth="true"/>
@@ -7922,19 +7642,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="379" t="s">
+      <c r="A1" s="369" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="371" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="371" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="371" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="371" t="s">
+      <c r="B1" s="361" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="361" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="361" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="361" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7942,16 +7662,16 @@
       <c r="A2" s="326" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="392" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="393" t="s">
+      <c r="B2" s="382" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="383" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="394" t="s">
+      <c r="D2" s="384" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="395" t="s">
+      <c r="E2" s="385" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7960,15 +7680,15 @@
         <v>1</v>
       </c>
       <c r="B3" s="332" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="396" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="397" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="398" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="386" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="387" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="388" t="s">
         <v>24</v>
       </c>
     </row>
@@ -7977,15 +7697,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="337" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="399" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="400" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="401" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="389" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="390" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="391" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7994,15 +7714,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="342" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="402" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="403" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="404" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="392" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="393" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="394" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8011,15 +7731,15 @@
         <v>1</v>
       </c>
       <c r="B6" s="347" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="405" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="406" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="407" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="395" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="396" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="397" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8028,15 +7748,15 @@
         <v>1</v>
       </c>
       <c r="B7" s="352" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="408" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="409" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="410" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="398" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="399" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="400" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8044,57 +7764,23 @@
       <c r="A8" s="356" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="357" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="411" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="412" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="413" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="361" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="362" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="414" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="415" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="416" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="366" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="425" t="s">
+      <c r="B8" s="409" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="420" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="420" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="420" t="s">
+      <c r="C8" s="404" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="404" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="404" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B8:E8"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/tabtools/demo/demo_survtab.xlsx
+++ b/tabtools/demo/demo_survtab.xlsx
@@ -134,7 +134,7 @@
     <t>5,185</t>
   </si>
   <si>
-    <t>Difference</t>
+    <t>Difference (SSRI - SNRI)</t>
   </si>
   <si>
     <t>39.0</t>
